--- a/data/clients_filtres.xlsx
+++ b/data/clients_filtres.xlsx
@@ -490,7 +490,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>+212772695559</t>
+          <t>+212770887143</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
